--- a/mode_docx_gen/pmi_tokz/part/lvnstoc/nsptoc1/NSPTOC1.xlsx
+++ b/mode_docx_gen/pmi_tokz/part/lvnstoc/nsptoc1/NSPTOC1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.11.240\Company\Ivanovo\Документация ЮНИТ М300\Разработка\Схемы ФБ ЮНИТ-М3\Трансформатор\ИЭУ Т 35 кВ Россети\01. Разработка ФБ\55. ЗОП\_xlsx\funcs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\www5\mode_docx_gen\pmi_tokz\part\lvnstoc\nsptoc1\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="110">
   <si>
     <t>Parameter</t>
   </si>
@@ -341,13 +341,22 @@
   </si>
   <si>
     <t>LVNSPTOC</t>
+  </si>
+  <si>
+    <t>alias</t>
+  </si>
+  <si>
+    <t>RatioSet</t>
+  </si>
+  <si>
+    <t>I2set</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,6 +376,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="8">
@@ -407,7 +423,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -430,11 +446,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -485,6 +523,12 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -791,7 +835,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:AE15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
@@ -810,7 +854,7 @@
     <col min="29" max="30" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -901,8 +945,11 @@
       <c r="AD1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="AE1" s="19" t="s">
+        <v>107</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>37</v>
       </c>
@@ -994,7 +1041,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>37</v>
       </c>
@@ -1086,7 +1133,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>37</v>
       </c>
@@ -1178,7 +1225,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>37</v>
       </c>
@@ -1270,7 +1317,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>37</v>
       </c>
@@ -1362,7 +1409,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>37</v>
       </c>
@@ -1454,7 +1501,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
@@ -1546,7 +1593,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>37</v>
       </c>
@@ -1638,7 +1685,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
@@ -1730,7 +1777,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>73</v>
       </c>
@@ -1822,7 +1869,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>73</v>
       </c>
@@ -1913,8 +1960,11 @@
       <c r="AD12" s="12" t="s">
         <v>40</v>
       </c>
+      <c r="AE12" s="20" t="s">
+        <v>109</v>
+      </c>
     </row>
-    <row r="13" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>73</v>
       </c>
@@ -2005,8 +2055,11 @@
       <c r="AD13" s="12" t="s">
         <v>40</v>
       </c>
+      <c r="AE13" t="s">
+        <v>108</v>
+      </c>
     </row>
-    <row r="14" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>73</v>
       </c>
@@ -2098,7 +2151,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:30" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>73</v>
       </c>
@@ -2188,6 +2241,9 @@
       </c>
       <c r="AD15" s="12" t="s">
         <v>40</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
